--- a/Detalle_Tecnicos_Reiterados.xlsx
+++ b/Detalle_Tecnicos_Reiterados.xlsx
@@ -1621,7 +1621,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46325.7397106482" recordCount="116">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="46326.4585300926" recordCount="116">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:I117" sheet="Detalle Actividad"/>
   </cacheSource>
